--- a/restaurant-tags.xlsx
+++ b/restaurant-tags.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="22">
   <si>
     <t>餐厅</t>
   </si>
@@ -41,7 +41,7 @@
     <t>有空调</t>
   </si>
   <si>
-    <t>列1</t>
+    <t>高消费一把</t>
   </si>
   <si>
     <t>苦瓜汤（烧腊饭）</t>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>淋汁（烧腊饭）</t>
+  </si>
+  <si>
+    <t>醉润香</t>
   </si>
 </sst>
 </file>
@@ -282,7 +285,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -292,6 +295,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F6556"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5F5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -651,7 +660,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -675,16 +684,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -693,90 +702,90 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -797,6 +806,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1076,13 +1088,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RestaurantTagsTable" displayName="RestaurantTagsTable" ref="A1:E15" totalsRowShown="0">
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RestaurantTagsTable" displayName="RestaurantTagsTable" ref="A1:D16" totalsRowShown="0">
+  <tableColumns count="4">
     <tableColumn id="1" name="餐厅"/>
     <tableColumn id="2" name="近距离"/>
     <tableColumn id="3" name="不吃饭（粥粉面）"/>
     <tableColumn id="4" name="有空调"/>
-    <tableColumn id="5" name="列1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1283,11 +1294,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="16.0288461538462" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5">
@@ -1545,9 +1557,26 @@
         <v>7</v>
       </c>
     </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B16:D200">
+    <dataValidation type="list" sqref="B17:D200">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
